--- a/temp_doc/PESERTA UJIAN FIX ADMIN.xlsx
+++ b/temp_doc/PESERTA UJIAN FIX ADMIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CED588-6B34-0B49-8575-741FA722F8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6BB00C-09D6-324F-9080-0BD50E9EB52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{A7D75AB7-B047-3448-8A7B-4FE35F9227AE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{A7D75AB7-B047-3448-8A7B-4FE35F9227AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$1108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$1107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3574,2230 +3574,2230 @@
     <t>XII TJKT 3</t>
   </si>
   <si>
-    <t>K01030098239820</t>
-  </si>
-  <si>
-    <t>K01030098259638</t>
-  </si>
-  <si>
-    <t>K01030098259639</t>
-  </si>
-  <si>
-    <t>K01030098259641</t>
-  </si>
-  <si>
-    <t>K01030098259642</t>
-  </si>
-  <si>
-    <t>K01030098259643</t>
-  </si>
-  <si>
-    <t>K01030098259644</t>
-  </si>
-  <si>
-    <t>K01030098259645</t>
-  </si>
-  <si>
-    <t>K01030098259646</t>
-  </si>
-  <si>
-    <t>K01030098259647</t>
-  </si>
-  <si>
-    <t>K01030098259648</t>
-  </si>
-  <si>
-    <t>K01030098259649</t>
-  </si>
-  <si>
-    <t>K01030098259650</t>
-  </si>
-  <si>
-    <t>K01030098259651</t>
-  </si>
-  <si>
-    <t>K01030098259653</t>
-  </si>
-  <si>
-    <t>K01030098259654</t>
-  </si>
-  <si>
-    <t>K01030098259821</t>
-  </si>
-  <si>
-    <t>K01030098259656</t>
-  </si>
-  <si>
-    <t>K01030098259810</t>
-  </si>
-  <si>
-    <t>K01030098259657</t>
-  </si>
-  <si>
-    <t>K01030098259658</t>
-  </si>
-  <si>
-    <t>K01030098259659</t>
-  </si>
-  <si>
-    <t>K01030098259660</t>
-  </si>
-  <si>
-    <t>K01030098259825</t>
-  </si>
-  <si>
-    <t>K01030098259661</t>
-  </si>
-  <si>
-    <t>K01030098259662</t>
-  </si>
-  <si>
-    <t>K01030098259663</t>
-  </si>
-  <si>
-    <t>K01030098259664</t>
-  </si>
-  <si>
-    <t>K01030098259665</t>
-  </si>
-  <si>
-    <t>K01030098259666</t>
-  </si>
-  <si>
-    <t>K01030098259667</t>
-  </si>
-  <si>
-    <t>K01030098259668</t>
-  </si>
-  <si>
-    <t>K01030098259669</t>
-  </si>
-  <si>
-    <t>K01030098259670</t>
-  </si>
-  <si>
-    <t>K01030098259671</t>
-  </si>
-  <si>
-    <t>K01030098259672</t>
-  </si>
-  <si>
-    <t>K01030098259673</t>
-  </si>
-  <si>
-    <t>K01030098259674</t>
-  </si>
-  <si>
-    <t>K01030098259675</t>
-  </si>
-  <si>
-    <t>K01030098259676</t>
-  </si>
-  <si>
-    <t>K01030098259677</t>
-  </si>
-  <si>
-    <t>K01030098259678</t>
-  </si>
-  <si>
-    <t>K01030098259680</t>
-  </si>
-  <si>
-    <t>K01030098259681</t>
-  </si>
-  <si>
-    <t>K01030098259683</t>
-  </si>
-  <si>
-    <t>K01030098259684</t>
-  </si>
-  <si>
-    <t>K01030098259685</t>
-  </si>
-  <si>
-    <t>K01030098259686</t>
-  </si>
-  <si>
-    <t>K01030098259687</t>
-  </si>
-  <si>
-    <t>K01030098259689</t>
-  </si>
-  <si>
-    <t>K01030098259690</t>
-  </si>
-  <si>
-    <t>K01030098259691</t>
-  </si>
-  <si>
-    <t>K01030098259598</t>
-  </si>
-  <si>
-    <t>K01030098259599</t>
-  </si>
-  <si>
-    <t>K01030098259600</t>
-  </si>
-  <si>
-    <t>K01030098259601</t>
-  </si>
-  <si>
-    <t>K01030098259602</t>
-  </si>
-  <si>
-    <t>K01030098259603</t>
-  </si>
-  <si>
-    <t>K01030098259604</t>
-  </si>
-  <si>
-    <t>K01030098259605</t>
-  </si>
-  <si>
-    <t>K01030098259606</t>
-  </si>
-  <si>
-    <t>K01030098259607</t>
-  </si>
-  <si>
-    <t>K01030098259608</t>
-  </si>
-  <si>
-    <t>K01030098259609</t>
-  </si>
-  <si>
-    <t>K01030098259812</t>
-  </si>
-  <si>
-    <t>K01030098259610</t>
-  </si>
-  <si>
-    <t>K01030098259611</t>
-  </si>
-  <si>
-    <t>K01030098259612</t>
-  </si>
-  <si>
-    <t>K01030098259613</t>
-  </si>
-  <si>
-    <t>K01030098259614</t>
-  </si>
-  <si>
-    <t>K01030098259811</t>
-  </si>
-  <si>
-    <t>K01030098259615</t>
-  </si>
-  <si>
-    <t>K01030098259616</t>
-  </si>
-  <si>
-    <t>K01030098259617</t>
-  </si>
-  <si>
-    <t>K01030098259618</t>
-  </si>
-  <si>
-    <t>K01030098259619</t>
-  </si>
-  <si>
-    <t>K01030098259620</t>
-  </si>
-  <si>
-    <t>K01030098259621</t>
-  </si>
-  <si>
-    <t>K01030098259622</t>
-  </si>
-  <si>
-    <t>K01030098259623</t>
-  </si>
-  <si>
-    <t>K01030098259624</t>
-  </si>
-  <si>
-    <t>K01030098259625</t>
-  </si>
-  <si>
-    <t>K01030098259626</t>
-  </si>
-  <si>
-    <t>K01030098259627</t>
-  </si>
-  <si>
-    <t>K01030098259628</t>
-  </si>
-  <si>
-    <t>K01030098259629</t>
-  </si>
-  <si>
-    <t>K01030098259630</t>
-  </si>
-  <si>
-    <t>K01030098259631</t>
-  </si>
-  <si>
-    <t>K01030098259632</t>
-  </si>
-  <si>
-    <t>K01030098259633</t>
-  </si>
-  <si>
-    <t>K01030098259634</t>
-  </si>
-  <si>
-    <t>K01030098259635</t>
-  </si>
-  <si>
-    <t>K01030098259637</t>
-  </si>
-  <si>
-    <t>K01030098259692</t>
-  </si>
-  <si>
-    <t>K01030098259693</t>
-  </si>
-  <si>
-    <t>K01030098259694</t>
-  </si>
-  <si>
-    <t>K01030098259695</t>
-  </si>
-  <si>
-    <t>K01030098259696</t>
-  </si>
-  <si>
-    <t>K01030098259697</t>
-  </si>
-  <si>
-    <t>K01030098259815</t>
-  </si>
-  <si>
-    <t>K01030098259698</t>
-  </si>
-  <si>
-    <t>K01030098259699</t>
-  </si>
-  <si>
-    <t>K01030098259700</t>
-  </si>
-  <si>
-    <t>K01030098259701</t>
-  </si>
-  <si>
-    <t>K01030098259702</t>
-  </si>
-  <si>
-    <t>K01030098259703</t>
-  </si>
-  <si>
-    <t>K01030098259704</t>
-  </si>
-  <si>
-    <t>K01030098259705</t>
-  </si>
-  <si>
-    <t>K01030098259706</t>
-  </si>
-  <si>
-    <t>K01030098259707</t>
-  </si>
-  <si>
-    <t>K01030098259708</t>
-  </si>
-  <si>
-    <t>K01030098259709</t>
-  </si>
-  <si>
-    <t>K01030098259710</t>
-  </si>
-  <si>
-    <t>K01030098259711</t>
-  </si>
-  <si>
-    <t>K01030098259712</t>
-  </si>
-  <si>
-    <t>K01030098259713</t>
-  </si>
-  <si>
-    <t>K01030098259714</t>
-  </si>
-  <si>
-    <t>K01030098259715</t>
-  </si>
-  <si>
-    <t>K01030098259716</t>
-  </si>
-  <si>
-    <t>K01030098259717</t>
-  </si>
-  <si>
-    <t>K01030098259718</t>
-  </si>
-  <si>
-    <t>K01030098259719</t>
-  </si>
-  <si>
-    <t>K01030098259720</t>
-  </si>
-  <si>
-    <t>K01030098259721</t>
-  </si>
-  <si>
-    <t>K01030098259722</t>
-  </si>
-  <si>
-    <t>K01030098259723</t>
-  </si>
-  <si>
-    <t>K01030098259724</t>
-  </si>
-  <si>
-    <t>K01030098259725</t>
-  </si>
-  <si>
-    <t>K01030098259726</t>
-  </si>
-  <si>
-    <t>K01030098259727</t>
-  </si>
-  <si>
-    <t>K01030098259728</t>
-  </si>
-  <si>
-    <t>K01030098259729</t>
-  </si>
-  <si>
-    <t>K01030098259730</t>
-  </si>
-  <si>
-    <t>K01030098259732</t>
-  </si>
-  <si>
-    <t>K01030098259733</t>
-  </si>
-  <si>
-    <t>K01030098259734</t>
-  </si>
-  <si>
-    <t>K01030098259735</t>
-  </si>
-  <si>
-    <t>K01030098259736</t>
-  </si>
-  <si>
-    <t>K01030098259737</t>
-  </si>
-  <si>
-    <t>K01030098259738</t>
-  </si>
-  <si>
-    <t>K01030098259739</t>
-  </si>
-  <si>
-    <t>K01030098259740</t>
-  </si>
-  <si>
-    <t>K01030098259741</t>
-  </si>
-  <si>
-    <t>K01030098259742</t>
-  </si>
-  <si>
-    <t>K01030098259743</t>
-  </si>
-  <si>
-    <t>K01030098259744</t>
-  </si>
-  <si>
-    <t>K01030098259745</t>
-  </si>
-  <si>
-    <t>K01030098259746</t>
-  </si>
-  <si>
-    <t>K01030098259747</t>
-  </si>
-  <si>
-    <t>K01030098259748</t>
-  </si>
-  <si>
-    <t>K01030098259749</t>
-  </si>
-  <si>
-    <t>K01030098259750</t>
-  </si>
-  <si>
-    <t>K01030098259751</t>
-  </si>
-  <si>
-    <t>K01030098259752</t>
-  </si>
-  <si>
-    <t>K01030098259753</t>
-  </si>
-  <si>
-    <t>K01030098259754</t>
-  </si>
-  <si>
-    <t>K01030098259755</t>
-  </si>
-  <si>
-    <t>K01030098259756</t>
-  </si>
-  <si>
-    <t>K01030098259757</t>
-  </si>
-  <si>
-    <t>K01030098259758</t>
-  </si>
-  <si>
-    <t>K01030098259759</t>
-  </si>
-  <si>
-    <t>K01030098259760</t>
-  </si>
-  <si>
-    <t>K01030098259761</t>
-  </si>
-  <si>
-    <t>K01030098259762</t>
-  </si>
-  <si>
-    <t>K01030098259763</t>
-  </si>
-  <si>
-    <t>K01030098259764</t>
-  </si>
-  <si>
-    <t>K01030098259765</t>
-  </si>
-  <si>
-    <t>K01030098259766</t>
-  </si>
-  <si>
-    <t>K01030098259767</t>
-  </si>
-  <si>
-    <t>K01030098259768</t>
-  </si>
-  <si>
-    <t>K01030098259769</t>
-  </si>
-  <si>
-    <t>K01030098259770</t>
-  </si>
-  <si>
-    <t>K01030098259771</t>
-  </si>
-  <si>
-    <t>K01030098259772</t>
-  </si>
-  <si>
-    <t>K01030098259773</t>
-  </si>
-  <si>
-    <t>K01030098259774</t>
-  </si>
-  <si>
-    <t>K01030098259775</t>
-  </si>
-  <si>
-    <t>K01030098259776</t>
-  </si>
-  <si>
-    <t>K01030098259777</t>
-  </si>
-  <si>
-    <t>K01030098259778</t>
-  </si>
-  <si>
-    <t>K01030098259779</t>
-  </si>
-  <si>
-    <t>K01030098259780</t>
-  </si>
-  <si>
-    <t>K01030098259781</t>
-  </si>
-  <si>
-    <t>K01030098259782</t>
-  </si>
-  <si>
-    <t>K01030098259783</t>
-  </si>
-  <si>
-    <t>K01030098259784</t>
-  </si>
-  <si>
-    <t>K01030098259785</t>
-  </si>
-  <si>
-    <t>K01030098259786</t>
-  </si>
-  <si>
-    <t>K01030098259787</t>
-  </si>
-  <si>
-    <t>K01030098259788</t>
-  </si>
-  <si>
-    <t>K01030098259789</t>
-  </si>
-  <si>
-    <t>K01030098259790</t>
-  </si>
-  <si>
-    <t>K01030098259791</t>
-  </si>
-  <si>
-    <t>K01030098259813</t>
-  </si>
-  <si>
-    <t>K01030098259792</t>
-  </si>
-  <si>
-    <t>K01030098259793</t>
-  </si>
-  <si>
-    <t>K01030098259794</t>
-  </si>
-  <si>
-    <t>K01030098259795</t>
-  </si>
-  <si>
-    <t>K01030098259796</t>
-  </si>
-  <si>
-    <t>K01030098259798</t>
-  </si>
-  <si>
-    <t>K01030098259799</t>
-  </si>
-  <si>
-    <t>K01030098259800</t>
-  </si>
-  <si>
-    <t>K01030098259801</t>
-  </si>
-  <si>
-    <t>K01030098259802</t>
-  </si>
-  <si>
-    <t>K01030098259803</t>
-  </si>
-  <si>
-    <t>K01030098259804</t>
-  </si>
-  <si>
-    <t>K01030098259805</t>
-  </si>
-  <si>
-    <t>K01030098259806</t>
-  </si>
-  <si>
-    <t>K01030098259807</t>
-  </si>
-  <si>
-    <t>K01030098259808</t>
-  </si>
-  <si>
-    <t>K01030098259688</t>
-  </si>
-  <si>
-    <t>K01030098259809</t>
-  </si>
-  <si>
-    <t>K01030098259434</t>
-  </si>
-  <si>
-    <t>K01030098259435</t>
-  </si>
-  <si>
-    <t>K01030098259436</t>
-  </si>
-  <si>
-    <t>K01030098259437</t>
-  </si>
-  <si>
-    <t>K01030098259438</t>
-  </si>
-  <si>
-    <t>K01030098259439</t>
-  </si>
-  <si>
-    <t>K01030098259440</t>
-  </si>
-  <si>
-    <t>K01030098259441</t>
-  </si>
-  <si>
-    <t>K01030098259442</t>
-  </si>
-  <si>
-    <t>K01030098259443</t>
-  </si>
-  <si>
-    <t>K01030098259444</t>
-  </si>
-  <si>
-    <t>K01030098259445</t>
-  </si>
-  <si>
-    <t>K01030098259446</t>
-  </si>
-  <si>
-    <t>K01030098259447</t>
-  </si>
-  <si>
-    <t>K01030098259448</t>
-  </si>
-  <si>
-    <t>K01030098259449</t>
-  </si>
-  <si>
-    <t>K01030098259450</t>
-  </si>
-  <si>
-    <t>K01030098259451</t>
-  </si>
-  <si>
-    <t>K01030098259452</t>
-  </si>
-  <si>
-    <t>K01030098259453</t>
-  </si>
-  <si>
-    <t>K01030098259454</t>
-  </si>
-  <si>
-    <t>K01030098259455</t>
-  </si>
-  <si>
-    <t>K01030098259456</t>
-  </si>
-  <si>
-    <t>K01030098259457</t>
-  </si>
-  <si>
-    <t>K01030098259458</t>
-  </si>
-  <si>
-    <t>K01030098259459</t>
-  </si>
-  <si>
-    <t>K01030098259460</t>
-  </si>
-  <si>
-    <t>K01030098259461</t>
-  </si>
-  <si>
-    <t>K01030098259462</t>
-  </si>
-  <si>
-    <t>K01030098259463</t>
-  </si>
-  <si>
-    <t>K01030098259464</t>
-  </si>
-  <si>
-    <t>K01030098259465</t>
-  </si>
-  <si>
-    <t>K01030098259466</t>
-  </si>
-  <si>
-    <t>K01030098259467</t>
-  </si>
-  <si>
-    <t>K01030098259468</t>
-  </si>
-  <si>
-    <t>K01030098259469</t>
-  </si>
-  <si>
-    <t>K01030098259470</t>
-  </si>
-  <si>
-    <t>K01030098259471</t>
-  </si>
-  <si>
-    <t>K01030098259472</t>
-  </si>
-  <si>
-    <t>K01030098259473</t>
-  </si>
-  <si>
-    <t>K01030098259474</t>
-  </si>
-  <si>
-    <t>K01030098259475</t>
-  </si>
-  <si>
-    <t>K01030098259476</t>
-  </si>
-  <si>
-    <t>K01030098259477</t>
-  </si>
-  <si>
-    <t>K01030098259478</t>
-  </si>
-  <si>
-    <t>K01030098259479</t>
-  </si>
-  <si>
-    <t>K01030098259480</t>
-  </si>
-  <si>
-    <t>K01030098259481</t>
-  </si>
-  <si>
-    <t>K01030098259482</t>
-  </si>
-  <si>
-    <t>K01030098259483</t>
-  </si>
-  <si>
-    <t>K01030098259484</t>
-  </si>
-  <si>
-    <t>K01030098259485</t>
-  </si>
-  <si>
-    <t>K01030098259486</t>
-  </si>
-  <si>
-    <t>K01030098259487</t>
-  </si>
-  <si>
-    <t>K01030098259489</t>
-  </si>
-  <si>
-    <t>K01030098259490</t>
-  </si>
-  <si>
-    <t>K01030098259491</t>
-  </si>
-  <si>
-    <t>K01030098259493</t>
-  </si>
-  <si>
-    <t>K01030098259494</t>
-  </si>
-  <si>
-    <t>K01030098259495</t>
-  </si>
-  <si>
-    <t>K01030098259497</t>
-  </si>
-  <si>
-    <t>K01030098259498</t>
-  </si>
-  <si>
-    <t>K01030098259499</t>
-  </si>
-  <si>
-    <t>K01030098259500</t>
-  </si>
-  <si>
-    <t>K01030098259496</t>
-  </si>
-  <si>
-    <t>K01030098259501</t>
-  </si>
-  <si>
-    <t>K01030098259502</t>
-  </si>
-  <si>
-    <t>K01030098259503</t>
-  </si>
-  <si>
-    <t>K01030098259504</t>
-  </si>
-  <si>
-    <t>K01030098259505</t>
-  </si>
-  <si>
-    <t>K01030098259506</t>
-  </si>
-  <si>
-    <t>K01030098259507</t>
-  </si>
-  <si>
-    <t>K01030098259508</t>
-  </si>
-  <si>
-    <t>K01030098259509</t>
-  </si>
-  <si>
-    <t>K01030098259510</t>
-  </si>
-  <si>
-    <t>K01030098259511</t>
-  </si>
-  <si>
-    <t>K01030098259512</t>
-  </si>
-  <si>
-    <t>K01030098259513</t>
-  </si>
-  <si>
-    <t>K01030098259515</t>
-  </si>
-  <si>
-    <t>K01030098259514</t>
-  </si>
-  <si>
-    <t>K01030098259516</t>
-  </si>
-  <si>
-    <t>K01030098259517</t>
-  </si>
-  <si>
-    <t>K01030098259518</t>
-  </si>
-  <si>
-    <t>K01030098259519</t>
-  </si>
-  <si>
-    <t>K01030098259520</t>
-  </si>
-  <si>
-    <t>K01030098259521</t>
-  </si>
-  <si>
-    <t>K01030098259524</t>
-  </si>
-  <si>
-    <t>K01030098259525</t>
-  </si>
-  <si>
-    <t>K01030098259526</t>
-  </si>
-  <si>
-    <t>K01030098259527</t>
-  </si>
-  <si>
-    <t>K01030098259528</t>
-  </si>
-  <si>
-    <t>K01030098259529</t>
-  </si>
-  <si>
-    <t>K01030098259530</t>
-  </si>
-  <si>
-    <t>K01030098259531</t>
-  </si>
-  <si>
-    <t>K01030098259532</t>
-  </si>
-  <si>
-    <t>K01030098259533</t>
-  </si>
-  <si>
-    <t>K01030098259538</t>
-  </si>
-  <si>
-    <t>K01030098259534</t>
-  </si>
-  <si>
-    <t>K01030098259535</t>
-  </si>
-  <si>
-    <t>K01030098259536</t>
-  </si>
-  <si>
-    <t>K01030098259537</t>
-  </si>
-  <si>
-    <t>K01030098259539</t>
-  </si>
-  <si>
-    <t>K01030098259540</t>
-  </si>
-  <si>
-    <t>K01030098259541</t>
-  </si>
-  <si>
-    <t>K01030098259542</t>
-  </si>
-  <si>
-    <t>K01030098259543</t>
-  </si>
-  <si>
-    <t>K01030098259544</t>
-  </si>
-  <si>
-    <t>K01030098259545</t>
-  </si>
-  <si>
-    <t>K01030098259546</t>
-  </si>
-  <si>
-    <t>K01030098259548</t>
-  </si>
-  <si>
-    <t>K01030098259549</t>
-  </si>
-  <si>
-    <t>K01030098259550</t>
-  </si>
-  <si>
-    <t>K01030098259551</t>
-  </si>
-  <si>
-    <t>K01030098259552</t>
-  </si>
-  <si>
-    <t>K01030098259554</t>
-  </si>
-  <si>
-    <t>K01030098259555</t>
-  </si>
-  <si>
-    <t>K01030098259556</t>
-  </si>
-  <si>
-    <t>K01030098259557</t>
-  </si>
-  <si>
-    <t>K01030098259558</t>
-  </si>
-  <si>
-    <t>K01030098259559</t>
-  </si>
-  <si>
-    <t>K01030098259560</t>
-  </si>
-  <si>
-    <t>K01030098259561</t>
-  </si>
-  <si>
-    <t>K01030098259562</t>
-  </si>
-  <si>
-    <t>K01030098259563</t>
-  </si>
-  <si>
-    <t>K01030098259564</t>
-  </si>
-  <si>
-    <t>K01030098259565</t>
-  </si>
-  <si>
-    <t>K01030098259566</t>
-  </si>
-  <si>
-    <t>K01030098259567</t>
-  </si>
-  <si>
-    <t>K01030098259568</t>
-  </si>
-  <si>
-    <t>K01030098259569</t>
-  </si>
-  <si>
-    <t>K01030098259570</t>
-  </si>
-  <si>
-    <t>K01030098259571</t>
-  </si>
-  <si>
-    <t>K01030098259572</t>
-  </si>
-  <si>
-    <t>K01030098259573</t>
-  </si>
-  <si>
-    <t>K01030098259574</t>
-  </si>
-  <si>
-    <t>K01030098259575</t>
-  </si>
-  <si>
-    <t>K01030098259576</t>
-  </si>
-  <si>
-    <t>K01030098259577</t>
-  </si>
-  <si>
-    <t>K01030098259579</t>
-  </si>
-  <si>
-    <t>K01030098259580</t>
-  </si>
-  <si>
-    <t>K01030098259578</t>
-  </si>
-  <si>
-    <t>K01030098259581</t>
-  </si>
-  <si>
-    <t>K01030098259582</t>
-  </si>
-  <si>
-    <t>K01030098259583</t>
-  </si>
-  <si>
-    <t>K01030098259584</t>
-  </si>
-  <si>
-    <t>K01030098259585</t>
-  </si>
-  <si>
-    <t>K01030098259586</t>
-  </si>
-  <si>
-    <t>K01030098259587</t>
-  </si>
-  <si>
-    <t>K01030098259588</t>
-  </si>
-  <si>
-    <t>K01030098259589</t>
-  </si>
-  <si>
-    <t>K01030098259590</t>
-  </si>
-  <si>
-    <t>K01030098259591</t>
-  </si>
-  <si>
-    <t>K01030098259592</t>
-  </si>
-  <si>
-    <t>K01030098259593</t>
-  </si>
-  <si>
-    <t>K01030098259594</t>
-  </si>
-  <si>
-    <t>K01030098259595</t>
-  </si>
-  <si>
-    <t>K01030098259596</t>
-  </si>
-  <si>
-    <t>K01030098259597</t>
-  </si>
-  <si>
-    <t>K01030098249238</t>
-  </si>
-  <si>
-    <t>K01030098249240</t>
-  </si>
-  <si>
-    <t>K01030098249246</t>
-  </si>
-  <si>
-    <t>K01030098249249</t>
-  </si>
-  <si>
-    <t>K01030098249250</t>
-  </si>
-  <si>
-    <t>K01030098249251</t>
-  </si>
-  <si>
-    <t>K01030098249255</t>
-  </si>
-  <si>
-    <t>K01030098249256</t>
-  </si>
-  <si>
-    <t>K01030098249260</t>
-  </si>
-  <si>
-    <t>K01030098249264</t>
-  </si>
-  <si>
-    <t>K01030098249270</t>
-  </si>
-  <si>
-    <t>K01030098249275</t>
-  </si>
-  <si>
-    <t>K01030098249277</t>
-  </si>
-  <si>
-    <t>K01030098249278</t>
-  </si>
-  <si>
-    <t>K01030098249279</t>
-  </si>
-  <si>
-    <t>K01030098249280</t>
-  </si>
-  <si>
-    <t>K01030098249281</t>
-  </si>
-  <si>
-    <t>K01030098249282</t>
-  </si>
-  <si>
-    <t>K01030098249284</t>
-  </si>
-  <si>
-    <t>K01030098249289</t>
-  </si>
-  <si>
-    <t>K01030098249287</t>
-  </si>
-  <si>
-    <t>K01030098249288</t>
-  </si>
-  <si>
-    <t>K01030098249290</t>
-  </si>
-  <si>
-    <t>K01030098249292</t>
-  </si>
-  <si>
-    <t>K01030098249293</t>
-  </si>
-  <si>
-    <t>K01030098249295</t>
-  </si>
-  <si>
-    <t>K01030098249297</t>
-  </si>
-  <si>
-    <t>K01030098249300</t>
-  </si>
-  <si>
-    <t>K01030098249301</t>
-  </si>
-  <si>
-    <t>K01030098249302</t>
-  </si>
-  <si>
-    <t>K01030098249239</t>
-  </si>
-  <si>
-    <t>K01030098249242</t>
-  </si>
-  <si>
-    <t>K01030098249243</t>
-  </si>
-  <si>
-    <t>K01030098249244</t>
-  </si>
-  <si>
-    <t>K01030098249245</t>
-  </si>
-  <si>
-    <t>K01030098249247</t>
-  </si>
-  <si>
-    <t>K01030098249252</t>
-  </si>
-  <si>
-    <t>K01030098249824</t>
-  </si>
-  <si>
-    <t>K01030098249253</t>
-  </si>
-  <si>
-    <t>K01030098249254</t>
-  </si>
-  <si>
-    <t>K01030098249257</t>
-  </si>
-  <si>
-    <t>K01030098249258</t>
-  </si>
-  <si>
-    <t>K01030098249259</t>
-  </si>
-  <si>
-    <t>K01030098249262</t>
-  </si>
-  <si>
-    <t>K01030098249266</t>
-  </si>
-  <si>
-    <t>K01030098249267</t>
-  </si>
-  <si>
-    <t>K01030098249268</t>
-  </si>
-  <si>
-    <t>K01030098249269</t>
-  </si>
-  <si>
-    <t>K01030098249271</t>
-  </si>
-  <si>
-    <t>K01030098249272</t>
-  </si>
-  <si>
-    <t>K01030098249274</t>
-  </si>
-  <si>
-    <t>K01030098249276</t>
-  </si>
-  <si>
-    <t>K01030098249283</t>
-  </si>
-  <si>
-    <t>K01030098249285</t>
-  </si>
-  <si>
-    <t>K01030098249286</t>
-  </si>
-  <si>
-    <t>K01030098249291</t>
-  </si>
-  <si>
-    <t>K01030098249294</t>
-  </si>
-  <si>
-    <t>K01030098249296</t>
-  </si>
-  <si>
-    <t>K01030098249298</t>
-  </si>
-  <si>
-    <t>K01030098249299</t>
-  </si>
-  <si>
-    <t>K01030098249192</t>
-  </si>
-  <si>
-    <t>K01030098249193</t>
-  </si>
-  <si>
-    <t>K01030098249194</t>
-  </si>
-  <si>
-    <t>K01030098249195</t>
-  </si>
-  <si>
-    <t>K01030098249196</t>
-  </si>
-  <si>
-    <t>K01030098249197</t>
-  </si>
-  <si>
-    <t>K01030098249198</t>
-  </si>
-  <si>
-    <t>K01030098249199</t>
-  </si>
-  <si>
-    <t>K01030098249200</t>
-  </si>
-  <si>
-    <t>K01030098249202</t>
-  </si>
-  <si>
-    <t>K01030098249203</t>
-  </si>
-  <si>
-    <t>K01030098249204</t>
-  </si>
-  <si>
-    <t>K01030098249205</t>
-  </si>
-  <si>
-    <t>K01030098249206</t>
-  </si>
-  <si>
-    <t>K01030098249207</t>
-  </si>
-  <si>
-    <t>K01030098249208</t>
-  </si>
-  <si>
-    <t>K01030098249209</t>
-  </si>
-  <si>
-    <t>K01030098239819</t>
-  </si>
-  <si>
-    <t>K01030098249210</t>
-  </si>
-  <si>
-    <t>K01030098249211</t>
-  </si>
-  <si>
-    <t>K01030098249212</t>
-  </si>
-  <si>
-    <t>K01030098249213</t>
-  </si>
-  <si>
-    <t>K01030098249214</t>
-  </si>
-  <si>
-    <t>K01030098249215</t>
-  </si>
-  <si>
-    <t>K01030098249216</t>
-  </si>
-  <si>
-    <t>K01030098249217</t>
-  </si>
-  <si>
-    <t>K01030098249218</t>
-  </si>
-  <si>
-    <t>K01030098249219</t>
-  </si>
-  <si>
-    <t>K01030098249220</t>
-  </si>
-  <si>
-    <t>K01030098249221</t>
-  </si>
-  <si>
-    <t>K01030098249222</t>
-  </si>
-  <si>
-    <t>K01030098249224</t>
-  </si>
-  <si>
-    <t>K01030098249225</t>
-  </si>
-  <si>
-    <t>K01030098249226</t>
-  </si>
-  <si>
-    <t>K01030098249227</t>
-  </si>
-  <si>
-    <t>K01030098249228</t>
-  </si>
-  <si>
-    <t>K01030098249229</t>
-  </si>
-  <si>
-    <t>K01030098249230</t>
-  </si>
-  <si>
-    <t>K01030098249231</t>
-  </si>
-  <si>
-    <t>K01030098249232</t>
-  </si>
-  <si>
-    <t>K01030098249233</t>
-  </si>
-  <si>
-    <t>K01030098249823</t>
-  </si>
-  <si>
-    <t>K01030098249234</t>
-  </si>
-  <si>
-    <t>K01030098249235</t>
-  </si>
-  <si>
-    <t>K01030098249236</t>
-  </si>
-  <si>
-    <t>K01030098249237</t>
-  </si>
-  <si>
-    <t>K01030098249303</t>
-  </si>
-  <si>
-    <t>K01030098249309</t>
-  </si>
-  <si>
-    <t>K01030098249312</t>
-  </si>
-  <si>
-    <t>K01030098249314</t>
-  </si>
-  <si>
-    <t>K01030098249816</t>
-  </si>
-  <si>
-    <t>K01030098249316</t>
-  </si>
-  <si>
-    <t>K01030098249317</t>
-  </si>
-  <si>
-    <t>K01030098249319</t>
-  </si>
-  <si>
-    <t>K01030098249323</t>
-  </si>
-  <si>
-    <t>K01030098249326</t>
-  </si>
-  <si>
-    <t>K01030098249330</t>
-  </si>
-  <si>
-    <t>K01030098249332</t>
-  </si>
-  <si>
-    <t>K01030098249335</t>
-  </si>
-  <si>
-    <t>K01030098249336</t>
-  </si>
-  <si>
-    <t>K01030098249338</t>
-  </si>
-  <si>
-    <t>K01030098249339</t>
-  </si>
-  <si>
-    <t>K01030098249342</t>
-  </si>
-  <si>
-    <t>K01030098249343</t>
-  </si>
-  <si>
-    <t>K01030098249344</t>
-  </si>
-  <si>
-    <t>K01030098249345</t>
-  </si>
-  <si>
-    <t>K01030098249347</t>
-  </si>
-  <si>
-    <t>K01030098249351</t>
-  </si>
-  <si>
-    <t>K01030098249354</t>
-  </si>
-  <si>
-    <t>K01030098249356</t>
-  </si>
-  <si>
-    <t>K01030098249357</t>
-  </si>
-  <si>
-    <t>K01030098249359</t>
-  </si>
-  <si>
-    <t>K01030098249360</t>
-  </si>
-  <si>
-    <t>K01030098249361</t>
-  </si>
-  <si>
-    <t>K01030098249364</t>
-  </si>
-  <si>
-    <t>K01030098249367</t>
-  </si>
-  <si>
-    <t>K01030098249365</t>
-  </si>
-  <si>
-    <t>K01030098249368</t>
-  </si>
-  <si>
-    <t>K01030098249370</t>
-  </si>
-  <si>
-    <t>K01030098249372</t>
-  </si>
-  <si>
-    <t>K01030098249373</t>
-  </si>
-  <si>
-    <t>K01030098249377</t>
-  </si>
-  <si>
-    <t>K01030098249378</t>
-  </si>
-  <si>
-    <t>K01030098249381</t>
-  </si>
-  <si>
-    <t>K01030098249383</t>
-  </si>
-  <si>
-    <t>K01030098249386</t>
-  </si>
-  <si>
-    <t>K01030098249304</t>
-  </si>
-  <si>
-    <t>K01030098249305</t>
-  </si>
-  <si>
-    <t>K01030098249306</t>
-  </si>
-  <si>
-    <t>K01030098249307</t>
-  </si>
-  <si>
-    <t>K01030098249308</t>
-  </si>
-  <si>
-    <t>K01030098249310</t>
-  </si>
-  <si>
-    <t>K01030098249313</t>
-  </si>
-  <si>
-    <t>K01030098249315</t>
-  </si>
-  <si>
-    <t>K01030098249318</t>
-  </si>
-  <si>
-    <t>K01030098249320</t>
-  </si>
-  <si>
-    <t>K01030098249321</t>
-  </si>
-  <si>
-    <t>K01030098249324</t>
-  </si>
-  <si>
-    <t>K01030098249325</t>
-  </si>
-  <si>
-    <t>K01030098249327</t>
-  </si>
-  <si>
-    <t>K01030098249328</t>
-  </si>
-  <si>
-    <t>K01030098249329</t>
-  </si>
-  <si>
-    <t>K01030098249331</t>
-  </si>
-  <si>
-    <t>K01030098249333</t>
-  </si>
-  <si>
-    <t>K01030098249334</t>
-  </si>
-  <si>
-    <t>K01030098249337</t>
-  </si>
-  <si>
-    <t>K01030098249340</t>
-  </si>
-  <si>
-    <t>K01030098249341</t>
-  </si>
-  <si>
-    <t>K01030098249346</t>
-  </si>
-  <si>
-    <t>K01030098249348</t>
-  </si>
-  <si>
-    <t>K01030098249350</t>
-  </si>
-  <si>
-    <t>K01030098249352</t>
-  </si>
-  <si>
-    <t>K01030098249353</t>
-  </si>
-  <si>
-    <t>K01030098249358</t>
-  </si>
-  <si>
-    <t>K01030098249362</t>
-  </si>
-  <si>
-    <t>K01030098249363</t>
-  </si>
-  <si>
-    <t>K01030098249366</t>
-  </si>
-  <si>
-    <t>K01030098249369</t>
-  </si>
-  <si>
-    <t>K01030098249371</t>
-  </si>
-  <si>
-    <t>K01030098249374</t>
-  </si>
-  <si>
-    <t>K01030098249375</t>
-  </si>
-  <si>
-    <t>K01030098249379</t>
-  </si>
-  <si>
-    <t>K01030098249380</t>
-  </si>
-  <si>
-    <t>K01030098249382</t>
-  </si>
-  <si>
-    <t>K01030098249385</t>
-  </si>
-  <si>
-    <t>K01030098249387</t>
-  </si>
-  <si>
-    <t>K01030098249388</t>
-  </si>
-  <si>
-    <t>K01030098249389</t>
-  </si>
-  <si>
-    <t>K01030098249390</t>
-  </si>
-  <si>
-    <t>K01030098249391</t>
-  </si>
-  <si>
-    <t>K01030098249392</t>
-  </si>
-  <si>
-    <t>K01030098249393</t>
-  </si>
-  <si>
-    <t>K01030098249394</t>
-  </si>
-  <si>
-    <t>K01030098249397</t>
-  </si>
-  <si>
-    <t>K01030098249398</t>
-  </si>
-  <si>
-    <t>K01030098249399</t>
-  </si>
-  <si>
-    <t>K01030098249400</t>
-  </si>
-  <si>
-    <t>K01030098249401</t>
-  </si>
-  <si>
-    <t>K01030098249402</t>
-  </si>
-  <si>
-    <t>K01030098249403</t>
-  </si>
-  <si>
-    <t>K01030098249404</t>
-  </si>
-  <si>
-    <t>K01030098249405</t>
-  </si>
-  <si>
-    <t>K01030098249406</t>
-  </si>
-  <si>
-    <t>K01030098249407</t>
-  </si>
-  <si>
-    <t>K01030098249409</t>
-  </si>
-  <si>
-    <t>K01030098249410</t>
-  </si>
-  <si>
-    <t>K01030098249413</t>
-  </si>
-  <si>
-    <t>K01030098249408</t>
-  </si>
-  <si>
-    <t>K01030098249412</t>
-  </si>
-  <si>
-    <t>K01030098249415</t>
-  </si>
-  <si>
-    <t>K01030098249416</t>
-  </si>
-  <si>
-    <t>K01030098249417</t>
-  </si>
-  <si>
-    <t>K01030098249432</t>
-  </si>
-  <si>
-    <t>K01030098249418</t>
-  </si>
-  <si>
-    <t>K01030098249419</t>
-  </si>
-  <si>
-    <t>K01030098249420</t>
-  </si>
-  <si>
-    <t>K01030098249421</t>
-  </si>
-  <si>
-    <t>K01030098249422</t>
-  </si>
-  <si>
-    <t>K01030098249423</t>
-  </si>
-  <si>
-    <t>K01030098249424</t>
-  </si>
-  <si>
-    <t>K01030098249426</t>
-  </si>
-  <si>
-    <t>K01030098249427</t>
-  </si>
-  <si>
-    <t>K01030098249428</t>
-  </si>
-  <si>
-    <t>K01030098249429</t>
-  </si>
-  <si>
-    <t>K01030098249430</t>
-  </si>
-  <si>
-    <t>K01030098249431</t>
-  </si>
-  <si>
-    <t>K01030098249058</t>
-  </si>
-  <si>
-    <t>K01030098249068</t>
-  </si>
-  <si>
-    <t>K01030098249069</t>
-  </si>
-  <si>
-    <t>K01030098249073</t>
-  </si>
-  <si>
-    <t>K01030098249074</t>
-  </si>
-  <si>
-    <t>K01030098249078</t>
-  </si>
-  <si>
-    <t>K01030098249080</t>
-  </si>
-  <si>
-    <t>K01030098249083</t>
-  </si>
-  <si>
-    <t>K01030098249084</t>
-  </si>
-  <si>
-    <t>K01030098249085</t>
-  </si>
-  <si>
-    <t>K01030098249090</t>
-  </si>
-  <si>
-    <t>K01030098249093</t>
-  </si>
-  <si>
-    <t>K01030098249095</t>
-  </si>
-  <si>
-    <t>K01030098249102</t>
-  </si>
-  <si>
-    <t>K01030098249103</t>
-  </si>
-  <si>
-    <t>K01030098249108</t>
-  </si>
-  <si>
-    <t>K01030098249113</t>
-  </si>
-  <si>
-    <t>K01030098249114</t>
-  </si>
-  <si>
-    <t>K01030098249116</t>
-  </si>
-  <si>
-    <t>K01030098249119</t>
-  </si>
-  <si>
-    <t>K01030098249120</t>
-  </si>
-  <si>
-    <t>K01030098249121</t>
-  </si>
-  <si>
-    <t>K01030098249125</t>
-  </si>
-  <si>
-    <t>K01030098249126</t>
-  </si>
-  <si>
-    <t>K01030098249129</t>
-  </si>
-  <si>
-    <t>K01030098249150</t>
-  </si>
-  <si>
-    <t>K01030098249153</t>
-  </si>
-  <si>
-    <t>K01030098249154</t>
-  </si>
-  <si>
-    <t>K01030098249161</t>
-  </si>
-  <si>
-    <t>K01030098249162</t>
-  </si>
-  <si>
-    <t>K01030098249168</t>
-  </si>
-  <si>
-    <t>K01030098249169</t>
-  </si>
-  <si>
-    <t>K01030098249172</t>
-  </si>
-  <si>
-    <t>K01030098249173</t>
-  </si>
-  <si>
-    <t>K01030098249177</t>
-  </si>
-  <si>
-    <t>K01030098249181</t>
-  </si>
-  <si>
-    <t>K01030098249182</t>
-  </si>
-  <si>
-    <t>K01030098249183</t>
-  </si>
-  <si>
-    <t>K01030098249184</t>
-  </si>
-  <si>
-    <t>K01030098249185</t>
-  </si>
-  <si>
-    <t>K01030098249189</t>
-  </si>
-  <si>
-    <t>K01030098249433</t>
-  </si>
-  <si>
-    <t>K01030098249060</t>
-  </si>
-  <si>
-    <t>K01030098249062</t>
-  </si>
-  <si>
-    <t>K01030098249064</t>
-  </si>
-  <si>
-    <t>K01030098249065</t>
-  </si>
-  <si>
-    <t>K01030098249066</t>
-  </si>
-  <si>
-    <t>K01030098249077</t>
-  </si>
-  <si>
-    <t>K01030098249079</t>
-  </si>
-  <si>
-    <t>K01030098249086</t>
-  </si>
-  <si>
-    <t>K01030098249088</t>
-  </si>
-  <si>
-    <t>K01030098249096</t>
-  </si>
-  <si>
-    <t>K01030098249098</t>
-  </si>
-  <si>
-    <t>K01030098249100</t>
-  </si>
-  <si>
-    <t>K01030098249101</t>
-  </si>
-  <si>
-    <t>K01030098249106</t>
-  </si>
-  <si>
-    <t>K01030098249107</t>
-  </si>
-  <si>
-    <t>K01030098249109</t>
-  </si>
-  <si>
-    <t>K01030098249110</t>
-  </si>
-  <si>
-    <t>K01030098249111</t>
-  </si>
-  <si>
-    <t>K01030098249115</t>
-  </si>
-  <si>
-    <t>K01030098249118</t>
-  </si>
-  <si>
-    <t>K01030098249122</t>
-  </si>
-  <si>
-    <t>K01030098249127</t>
-  </si>
-  <si>
-    <t>K01030098249131</t>
-  </si>
-  <si>
-    <t>K01030098249139</t>
-  </si>
-  <si>
-    <t>K01030098249141</t>
-  </si>
-  <si>
-    <t>K01030098249142</t>
-  </si>
-  <si>
-    <t>K01030098249143</t>
-  </si>
-  <si>
-    <t>K01030098249145</t>
-  </si>
-  <si>
-    <t>K01030098249151</t>
-  </si>
-  <si>
-    <t>K01030098249152</t>
-  </si>
-  <si>
-    <t>K01030098249156</t>
-  </si>
-  <si>
-    <t>K01030098249158</t>
-  </si>
-  <si>
-    <t>K01030098249159</t>
-  </si>
-  <si>
-    <t>K01030098249166</t>
-  </si>
-  <si>
-    <t>K01030098249170</t>
-  </si>
-  <si>
-    <t>K01030098249174</t>
-  </si>
-  <si>
-    <t>K01030098249175</t>
-  </si>
-  <si>
-    <t>K01030098249176</t>
-  </si>
-  <si>
-    <t>K01030098249187</t>
-  </si>
-  <si>
-    <t>K01030098249190</t>
-  </si>
-  <si>
-    <t>K01030098249057</t>
-  </si>
-  <si>
-    <t>K01030098249059</t>
-  </si>
-  <si>
-    <t>K01030098249063</t>
-  </si>
-  <si>
-    <t>K01030098249067</t>
-  </si>
-  <si>
-    <t>K01030098249071</t>
-  </si>
-  <si>
-    <t>K01030098249072</t>
-  </si>
-  <si>
-    <t>K01030098249075</t>
-  </si>
-  <si>
-    <t>K01030098249076</t>
-  </si>
-  <si>
-    <t>K01030098249081</t>
-  </si>
-  <si>
-    <t>K01030098249082</t>
-  </si>
-  <si>
-    <t>K01030098249087</t>
-  </si>
-  <si>
-    <t>K01030098249089</t>
-  </si>
-  <si>
-    <t>K01030098249091</t>
-  </si>
-  <si>
-    <t>K01030098249092</t>
-  </si>
-  <si>
-    <t>K01030098249094</t>
-  </si>
-  <si>
-    <t>K01030098249097</t>
-  </si>
-  <si>
-    <t>K01030098249105</t>
-  </si>
-  <si>
-    <t>K01030098249112</t>
-  </si>
-  <si>
-    <t>K01030098249117</t>
-  </si>
-  <si>
-    <t>K01030098249123</t>
-  </si>
-  <si>
-    <t>K01030098249124</t>
-  </si>
-  <si>
-    <t>K01030098249132</t>
-  </si>
-  <si>
-    <t>K01030098249134</t>
-  </si>
-  <si>
-    <t>K01030098249135</t>
-  </si>
-  <si>
-    <t>K01030098249137</t>
-  </si>
-  <si>
-    <t>K01030098249138</t>
-  </si>
-  <si>
-    <t>K01030098249140</t>
-  </si>
-  <si>
-    <t>K01030098249128</t>
-  </si>
-  <si>
-    <t>K01030098249146</t>
-  </si>
-  <si>
-    <t>K01030098249147</t>
-  </si>
-  <si>
-    <t>K01030098249148</t>
-  </si>
-  <si>
-    <t>K01030098249149</t>
-  </si>
-  <si>
-    <t>K01030098249155</t>
-  </si>
-  <si>
-    <t>K01030098249157</t>
-  </si>
-  <si>
-    <t>K01030098249160</t>
-  </si>
-  <si>
-    <t>K01030098249163</t>
-  </si>
-  <si>
-    <t>K01030098249164</t>
-  </si>
-  <si>
-    <t>K01030098249167</t>
-  </si>
-  <si>
-    <t>K01030098249171</t>
-  </si>
-  <si>
-    <t>K01030098249178</t>
-  </si>
-  <si>
-    <t>K01030098249179</t>
-  </si>
-  <si>
-    <t>K01030098249180</t>
-  </si>
-  <si>
-    <t>K01030098249186</t>
-  </si>
-  <si>
-    <t>K01030098249188</t>
-  </si>
-  <si>
-    <t>CBT12345</t>
-  </si>
-  <si>
-    <t>X AKL 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>X AKL 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>X DKV_SAS_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>X PM_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 3_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 4_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI DKV_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI PM_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 3_SAS_2526</t>
+    <t>S1001</t>
+  </si>
+  <si>
+    <t>S1002</t>
+  </si>
+  <si>
+    <t>S1003</t>
+  </si>
+  <si>
+    <t>S1004</t>
+  </si>
+  <si>
+    <t>S1005</t>
+  </si>
+  <si>
+    <t>S1006</t>
+  </si>
+  <si>
+    <t>S1007</t>
+  </si>
+  <si>
+    <t>S1008</t>
+  </si>
+  <si>
+    <t>S1009</t>
+  </si>
+  <si>
+    <t>S1010</t>
+  </si>
+  <si>
+    <t>S1011</t>
+  </si>
+  <si>
+    <t>S1012</t>
+  </si>
+  <si>
+    <t>S1013</t>
+  </si>
+  <si>
+    <t>S1014</t>
+  </si>
+  <si>
+    <t>S1015</t>
+  </si>
+  <si>
+    <t>S1016</t>
+  </si>
+  <si>
+    <t>S1017</t>
+  </si>
+  <si>
+    <t>S1018</t>
+  </si>
+  <si>
+    <t>S1019</t>
+  </si>
+  <si>
+    <t>S1020</t>
+  </si>
+  <si>
+    <t>S1021</t>
+  </si>
+  <si>
+    <t>S1022</t>
+  </si>
+  <si>
+    <t>S1023</t>
+  </si>
+  <si>
+    <t>S1024</t>
+  </si>
+  <si>
+    <t>S1025</t>
+  </si>
+  <si>
+    <t>S1026</t>
+  </si>
+  <si>
+    <t>S1027</t>
+  </si>
+  <si>
+    <t>S1028</t>
+  </si>
+  <si>
+    <t>S1029</t>
+  </si>
+  <si>
+    <t>S1030</t>
+  </si>
+  <si>
+    <t>S1031</t>
+  </si>
+  <si>
+    <t>S1032</t>
+  </si>
+  <si>
+    <t>S1033</t>
+  </si>
+  <si>
+    <t>S1034</t>
+  </si>
+  <si>
+    <t>S1035</t>
+  </si>
+  <si>
+    <t>S1036</t>
+  </si>
+  <si>
+    <t>S1037</t>
+  </si>
+  <si>
+    <t>S1038</t>
+  </si>
+  <si>
+    <t>S1039</t>
+  </si>
+  <si>
+    <t>S1040</t>
+  </si>
+  <si>
+    <t>S1041</t>
+  </si>
+  <si>
+    <t>S1042</t>
+  </si>
+  <si>
+    <t>S1043</t>
+  </si>
+  <si>
+    <t>S1044</t>
+  </si>
+  <si>
+    <t>S1045</t>
+  </si>
+  <si>
+    <t>S1046</t>
+  </si>
+  <si>
+    <t>S1047</t>
+  </si>
+  <si>
+    <t>S1048</t>
+  </si>
+  <si>
+    <t>S1049</t>
+  </si>
+  <si>
+    <t>S1050</t>
+  </si>
+  <si>
+    <t>S1051</t>
+  </si>
+  <si>
+    <t>S1052</t>
+  </si>
+  <si>
+    <t>S1053</t>
+  </si>
+  <si>
+    <t>S1054</t>
+  </si>
+  <si>
+    <t>S1055</t>
+  </si>
+  <si>
+    <t>S1056</t>
+  </si>
+  <si>
+    <t>S1057</t>
+  </si>
+  <si>
+    <t>S1058</t>
+  </si>
+  <si>
+    <t>S1059</t>
+  </si>
+  <si>
+    <t>S1060</t>
+  </si>
+  <si>
+    <t>S1061</t>
+  </si>
+  <si>
+    <t>S1062</t>
+  </si>
+  <si>
+    <t>S1063</t>
+  </si>
+  <si>
+    <t>S1064</t>
+  </si>
+  <si>
+    <t>S1065</t>
+  </si>
+  <si>
+    <t>S1066</t>
+  </si>
+  <si>
+    <t>S1067</t>
+  </si>
+  <si>
+    <t>S1068</t>
+  </si>
+  <si>
+    <t>S1069</t>
+  </si>
+  <si>
+    <t>S1070</t>
+  </si>
+  <si>
+    <t>S1071</t>
+  </si>
+  <si>
+    <t>S1072</t>
+  </si>
+  <si>
+    <t>S1073</t>
+  </si>
+  <si>
+    <t>S1074</t>
+  </si>
+  <si>
+    <t>S1075</t>
+  </si>
+  <si>
+    <t>S1076</t>
+  </si>
+  <si>
+    <t>S1077</t>
+  </si>
+  <si>
+    <t>S1078</t>
+  </si>
+  <si>
+    <t>S1079</t>
+  </si>
+  <si>
+    <t>S1080</t>
+  </si>
+  <si>
+    <t>S1081</t>
+  </si>
+  <si>
+    <t>S1082</t>
+  </si>
+  <si>
+    <t>S1083</t>
+  </si>
+  <si>
+    <t>S1084</t>
+  </si>
+  <si>
+    <t>S1085</t>
+  </si>
+  <si>
+    <t>S1086</t>
+  </si>
+  <si>
+    <t>S1087</t>
+  </si>
+  <si>
+    <t>S1088</t>
+  </si>
+  <si>
+    <t>S1089</t>
+  </si>
+  <si>
+    <t>S1090</t>
+  </si>
+  <si>
+    <t>S1091</t>
+  </si>
+  <si>
+    <t>S1092</t>
+  </si>
+  <si>
+    <t>S1093</t>
+  </si>
+  <si>
+    <t>S1094</t>
+  </si>
+  <si>
+    <t>S1095</t>
+  </si>
+  <si>
+    <t>S1096</t>
+  </si>
+  <si>
+    <t>S1097</t>
+  </si>
+  <si>
+    <t>S1098</t>
+  </si>
+  <si>
+    <t>S1099</t>
+  </si>
+  <si>
+    <t>S1100</t>
+  </si>
+  <si>
+    <t>S1101</t>
+  </si>
+  <si>
+    <t>S1102</t>
+  </si>
+  <si>
+    <t>S1103</t>
+  </si>
+  <si>
+    <t>S1104</t>
+  </si>
+  <si>
+    <t>S1105</t>
+  </si>
+  <si>
+    <t>S1106</t>
+  </si>
+  <si>
+    <t>S1107</t>
+  </si>
+  <si>
+    <t>S1108</t>
+  </si>
+  <si>
+    <t>S1109</t>
+  </si>
+  <si>
+    <t>S1110</t>
+  </si>
+  <si>
+    <t>S1111</t>
+  </si>
+  <si>
+    <t>S1112</t>
+  </si>
+  <si>
+    <t>S1113</t>
+  </si>
+  <si>
+    <t>S1114</t>
+  </si>
+  <si>
+    <t>S1115</t>
+  </si>
+  <si>
+    <t>S1116</t>
+  </si>
+  <si>
+    <t>S1117</t>
+  </si>
+  <si>
+    <t>S1118</t>
+  </si>
+  <si>
+    <t>S1119</t>
+  </si>
+  <si>
+    <t>S1120</t>
+  </si>
+  <si>
+    <t>S1121</t>
+  </si>
+  <si>
+    <t>S1122</t>
+  </si>
+  <si>
+    <t>S1123</t>
+  </si>
+  <si>
+    <t>S1124</t>
+  </si>
+  <si>
+    <t>S1125</t>
+  </si>
+  <si>
+    <t>S1126</t>
+  </si>
+  <si>
+    <t>S1127</t>
+  </si>
+  <si>
+    <t>S1128</t>
+  </si>
+  <si>
+    <t>S1129</t>
+  </si>
+  <si>
+    <t>S1130</t>
+  </si>
+  <si>
+    <t>S1131</t>
+  </si>
+  <si>
+    <t>S1132</t>
+  </si>
+  <si>
+    <t>S1133</t>
+  </si>
+  <si>
+    <t>S1134</t>
+  </si>
+  <si>
+    <t>S1135</t>
+  </si>
+  <si>
+    <t>S1136</t>
+  </si>
+  <si>
+    <t>S1137</t>
+  </si>
+  <si>
+    <t>S1138</t>
+  </si>
+  <si>
+    <t>S1139</t>
+  </si>
+  <si>
+    <t>S1140</t>
+  </si>
+  <si>
+    <t>S1141</t>
+  </si>
+  <si>
+    <t>S1142</t>
+  </si>
+  <si>
+    <t>S1143</t>
+  </si>
+  <si>
+    <t>S1144</t>
+  </si>
+  <si>
+    <t>S1145</t>
+  </si>
+  <si>
+    <t>S1146</t>
+  </si>
+  <si>
+    <t>S1147</t>
+  </si>
+  <si>
+    <t>S1148</t>
+  </si>
+  <si>
+    <t>S1149</t>
+  </si>
+  <si>
+    <t>S1150</t>
+  </si>
+  <si>
+    <t>S1151</t>
+  </si>
+  <si>
+    <t>S1152</t>
+  </si>
+  <si>
+    <t>S1153</t>
+  </si>
+  <si>
+    <t>S1154</t>
+  </si>
+  <si>
+    <t>S1155</t>
+  </si>
+  <si>
+    <t>S1156</t>
+  </si>
+  <si>
+    <t>S1157</t>
+  </si>
+  <si>
+    <t>S1158</t>
+  </si>
+  <si>
+    <t>S1159</t>
+  </si>
+  <si>
+    <t>S1160</t>
+  </si>
+  <si>
+    <t>S1161</t>
+  </si>
+  <si>
+    <t>S1162</t>
+  </si>
+  <si>
+    <t>S1163</t>
+  </si>
+  <si>
+    <t>S1164</t>
+  </si>
+  <si>
+    <t>S1165</t>
+  </si>
+  <si>
+    <t>S1166</t>
+  </si>
+  <si>
+    <t>S1167</t>
+  </si>
+  <si>
+    <t>S1168</t>
+  </si>
+  <si>
+    <t>S1169</t>
+  </si>
+  <si>
+    <t>S1170</t>
+  </si>
+  <si>
+    <t>S1171</t>
+  </si>
+  <si>
+    <t>S1172</t>
+  </si>
+  <si>
+    <t>S1173</t>
+  </si>
+  <si>
+    <t>S1174</t>
+  </si>
+  <si>
+    <t>S1175</t>
+  </si>
+  <si>
+    <t>S1176</t>
+  </si>
+  <si>
+    <t>S1177</t>
+  </si>
+  <si>
+    <t>S1178</t>
+  </si>
+  <si>
+    <t>S1179</t>
+  </si>
+  <si>
+    <t>S1180</t>
+  </si>
+  <si>
+    <t>S1181</t>
+  </si>
+  <si>
+    <t>S1182</t>
+  </si>
+  <si>
+    <t>S1183</t>
+  </si>
+  <si>
+    <t>S1184</t>
+  </si>
+  <si>
+    <t>S1185</t>
+  </si>
+  <si>
+    <t>S1186</t>
+  </si>
+  <si>
+    <t>S1187</t>
+  </si>
+  <si>
+    <t>S1188</t>
+  </si>
+  <si>
+    <t>S1189</t>
+  </si>
+  <si>
+    <t>S1190</t>
+  </si>
+  <si>
+    <t>S1191</t>
+  </si>
+  <si>
+    <t>S1192</t>
+  </si>
+  <si>
+    <t>S1193</t>
+  </si>
+  <si>
+    <t>S1194</t>
+  </si>
+  <si>
+    <t>S1195</t>
+  </si>
+  <si>
+    <t>S1196</t>
+  </si>
+  <si>
+    <t>S1197</t>
+  </si>
+  <si>
+    <t>S1198</t>
+  </si>
+  <si>
+    <t>S1199</t>
+  </si>
+  <si>
+    <t>S1200</t>
+  </si>
+  <si>
+    <t>S1201</t>
+  </si>
+  <si>
+    <t>S1202</t>
+  </si>
+  <si>
+    <t>S1203</t>
+  </si>
+  <si>
+    <t>S1204</t>
+  </si>
+  <si>
+    <t>S1205</t>
+  </si>
+  <si>
+    <t>S1206</t>
+  </si>
+  <si>
+    <t>S1207</t>
+  </si>
+  <si>
+    <t>S1208</t>
+  </si>
+  <si>
+    <t>S1209</t>
+  </si>
+  <si>
+    <t>S1210</t>
+  </si>
+  <si>
+    <t>S1211</t>
+  </si>
+  <si>
+    <t>S1212</t>
+  </si>
+  <si>
+    <t>S1213</t>
+  </si>
+  <si>
+    <t>S1214</t>
+  </si>
+  <si>
+    <t>S1215</t>
+  </si>
+  <si>
+    <t>S1216</t>
+  </si>
+  <si>
+    <t>S1217</t>
+  </si>
+  <si>
+    <t>S1218</t>
+  </si>
+  <si>
+    <t>S1219</t>
+  </si>
+  <si>
+    <t>S1220</t>
+  </si>
+  <si>
+    <t>S1221</t>
+  </si>
+  <si>
+    <t>S1222</t>
+  </si>
+  <si>
+    <t>S1223</t>
+  </si>
+  <si>
+    <t>S1224</t>
+  </si>
+  <si>
+    <t>S1225</t>
+  </si>
+  <si>
+    <t>S1226</t>
+  </si>
+  <si>
+    <t>S1227</t>
+  </si>
+  <si>
+    <t>S1228</t>
+  </si>
+  <si>
+    <t>S1229</t>
+  </si>
+  <si>
+    <t>S1230</t>
+  </si>
+  <si>
+    <t>S1231</t>
+  </si>
+  <si>
+    <t>S1232</t>
+  </si>
+  <si>
+    <t>S1233</t>
+  </si>
+  <si>
+    <t>S1234</t>
+  </si>
+  <si>
+    <t>S1235</t>
+  </si>
+  <si>
+    <t>S1236</t>
+  </si>
+  <si>
+    <t>S1237</t>
+  </si>
+  <si>
+    <t>S1238</t>
+  </si>
+  <si>
+    <t>S1239</t>
+  </si>
+  <si>
+    <t>S1240</t>
+  </si>
+  <si>
+    <t>S1241</t>
+  </si>
+  <si>
+    <t>S1242</t>
+  </si>
+  <si>
+    <t>S1243</t>
+  </si>
+  <si>
+    <t>S1244</t>
+  </si>
+  <si>
+    <t>S1245</t>
+  </si>
+  <si>
+    <t>S1246</t>
+  </si>
+  <si>
+    <t>S1247</t>
+  </si>
+  <si>
+    <t>S1248</t>
+  </si>
+  <si>
+    <t>S1249</t>
+  </si>
+  <si>
+    <t>S1250</t>
+  </si>
+  <si>
+    <t>S1251</t>
+  </si>
+  <si>
+    <t>S1252</t>
+  </si>
+  <si>
+    <t>S1253</t>
+  </si>
+  <si>
+    <t>S1254</t>
+  </si>
+  <si>
+    <t>S1255</t>
+  </si>
+  <si>
+    <t>S1256</t>
+  </si>
+  <si>
+    <t>S1257</t>
+  </si>
+  <si>
+    <t>S1258</t>
+  </si>
+  <si>
+    <t>S1259</t>
+  </si>
+  <si>
+    <t>S1260</t>
+  </si>
+  <si>
+    <t>S1261</t>
+  </si>
+  <si>
+    <t>S1262</t>
+  </si>
+  <si>
+    <t>S1263</t>
+  </si>
+  <si>
+    <t>S1264</t>
+  </si>
+  <si>
+    <t>S1265</t>
+  </si>
+  <si>
+    <t>S1266</t>
+  </si>
+  <si>
+    <t>S1267</t>
+  </si>
+  <si>
+    <t>S1268</t>
+  </si>
+  <si>
+    <t>S1269</t>
+  </si>
+  <si>
+    <t>S1270</t>
+  </si>
+  <si>
+    <t>S1271</t>
+  </si>
+  <si>
+    <t>S1272</t>
+  </si>
+  <si>
+    <t>S1273</t>
+  </si>
+  <si>
+    <t>S1274</t>
+  </si>
+  <si>
+    <t>S1275</t>
+  </si>
+  <si>
+    <t>S1276</t>
+  </si>
+  <si>
+    <t>S1277</t>
+  </si>
+  <si>
+    <t>S1278</t>
+  </si>
+  <si>
+    <t>S1279</t>
+  </si>
+  <si>
+    <t>S1280</t>
+  </si>
+  <si>
+    <t>S1281</t>
+  </si>
+  <si>
+    <t>S1282</t>
+  </si>
+  <si>
+    <t>S1283</t>
+  </si>
+  <si>
+    <t>S1284</t>
+  </si>
+  <si>
+    <t>S1285</t>
+  </si>
+  <si>
+    <t>S1286</t>
+  </si>
+  <si>
+    <t>S1287</t>
+  </si>
+  <si>
+    <t>S1288</t>
+  </si>
+  <si>
+    <t>S1289</t>
+  </si>
+  <si>
+    <t>S1290</t>
+  </si>
+  <si>
+    <t>S1291</t>
+  </si>
+  <si>
+    <t>S1292</t>
+  </si>
+  <si>
+    <t>S1293</t>
+  </si>
+  <si>
+    <t>S1294</t>
+  </si>
+  <si>
+    <t>S1295</t>
+  </si>
+  <si>
+    <t>S1296</t>
+  </si>
+  <si>
+    <t>S1297</t>
+  </si>
+  <si>
+    <t>S1298</t>
+  </si>
+  <si>
+    <t>S1299</t>
+  </si>
+  <si>
+    <t>S1300</t>
+  </si>
+  <si>
+    <t>S1301</t>
+  </si>
+  <si>
+    <t>S1302</t>
+  </si>
+  <si>
+    <t>S1303</t>
+  </si>
+  <si>
+    <t>S1304</t>
+  </si>
+  <si>
+    <t>S1305</t>
+  </si>
+  <si>
+    <t>S1306</t>
+  </si>
+  <si>
+    <t>S1307</t>
+  </si>
+  <si>
+    <t>S1308</t>
+  </si>
+  <si>
+    <t>S1309</t>
+  </si>
+  <si>
+    <t>S1310</t>
+  </si>
+  <si>
+    <t>S1311</t>
+  </si>
+  <si>
+    <t>S1312</t>
+  </si>
+  <si>
+    <t>S1313</t>
+  </si>
+  <si>
+    <t>S1314</t>
+  </si>
+  <si>
+    <t>S1315</t>
+  </si>
+  <si>
+    <t>S1316</t>
+  </si>
+  <si>
+    <t>S1317</t>
+  </si>
+  <si>
+    <t>S1318</t>
+  </si>
+  <si>
+    <t>S1319</t>
+  </si>
+  <si>
+    <t>S1320</t>
+  </si>
+  <si>
+    <t>S1321</t>
+  </si>
+  <si>
+    <t>S1322</t>
+  </si>
+  <si>
+    <t>S1323</t>
+  </si>
+  <si>
+    <t>S1324</t>
+  </si>
+  <si>
+    <t>S1325</t>
+  </si>
+  <si>
+    <t>S1326</t>
+  </si>
+  <si>
+    <t>S1327</t>
+  </si>
+  <si>
+    <t>S1328</t>
+  </si>
+  <si>
+    <t>S1329</t>
+  </si>
+  <si>
+    <t>S1330</t>
+  </si>
+  <si>
+    <t>S1331</t>
+  </si>
+  <si>
+    <t>S1332</t>
+  </si>
+  <si>
+    <t>S1333</t>
+  </si>
+  <si>
+    <t>S1334</t>
+  </si>
+  <si>
+    <t>S1335</t>
+  </si>
+  <si>
+    <t>S1336</t>
+  </si>
+  <si>
+    <t>S1337</t>
+  </si>
+  <si>
+    <t>S1338</t>
+  </si>
+  <si>
+    <t>S1339</t>
+  </si>
+  <si>
+    <t>S1340</t>
+  </si>
+  <si>
+    <t>S1341</t>
+  </si>
+  <si>
+    <t>S1342</t>
+  </si>
+  <si>
+    <t>S1343</t>
+  </si>
+  <si>
+    <t>S1344</t>
+  </si>
+  <si>
+    <t>S1345</t>
+  </si>
+  <si>
+    <t>S1346</t>
+  </si>
+  <si>
+    <t>S1347</t>
+  </si>
+  <si>
+    <t>S1348</t>
+  </si>
+  <si>
+    <t>S1349</t>
+  </si>
+  <si>
+    <t>S1350</t>
+  </si>
+  <si>
+    <t>S1351</t>
+  </si>
+  <si>
+    <t>S1352</t>
+  </si>
+  <si>
+    <t>S1353</t>
+  </si>
+  <si>
+    <t>S1354</t>
+  </si>
+  <si>
+    <t>S1355</t>
+  </si>
+  <si>
+    <t>S1356</t>
+  </si>
+  <si>
+    <t>S1357</t>
+  </si>
+  <si>
+    <t>S1358</t>
+  </si>
+  <si>
+    <t>S1359</t>
+  </si>
+  <si>
+    <t>S1360</t>
+  </si>
+  <si>
+    <t>S1361</t>
+  </si>
+  <si>
+    <t>S1362</t>
+  </si>
+  <si>
+    <t>S1363</t>
+  </si>
+  <si>
+    <t>S1364</t>
+  </si>
+  <si>
+    <t>S1365</t>
+  </si>
+  <si>
+    <t>S1366</t>
+  </si>
+  <si>
+    <t>S1367</t>
+  </si>
+  <si>
+    <t>S1368</t>
+  </si>
+  <si>
+    <t>S1369</t>
+  </si>
+  <si>
+    <t>S1370</t>
+  </si>
+  <si>
+    <t>S1371</t>
+  </si>
+  <si>
+    <t>S1372</t>
+  </si>
+  <si>
+    <t>S1373</t>
+  </si>
+  <si>
+    <t>S1374</t>
+  </si>
+  <si>
+    <t>S1375</t>
+  </si>
+  <si>
+    <t>S1376</t>
+  </si>
+  <si>
+    <t>S1377</t>
+  </si>
+  <si>
+    <t>S1378</t>
+  </si>
+  <si>
+    <t>S1379</t>
+  </si>
+  <si>
+    <t>S1380</t>
+  </si>
+  <si>
+    <t>S1381</t>
+  </si>
+  <si>
+    <t>S1382</t>
+  </si>
+  <si>
+    <t>S1383</t>
+  </si>
+  <si>
+    <t>S1384</t>
+  </si>
+  <si>
+    <t>S1385</t>
+  </si>
+  <si>
+    <t>S1386</t>
+  </si>
+  <si>
+    <t>S1387</t>
+  </si>
+  <si>
+    <t>S1388</t>
+  </si>
+  <si>
+    <t>S1389</t>
+  </si>
+  <si>
+    <t>S1390</t>
+  </si>
+  <si>
+    <t>S1391</t>
+  </si>
+  <si>
+    <t>S1392</t>
+  </si>
+  <si>
+    <t>S1393</t>
+  </si>
+  <si>
+    <t>S1394</t>
+  </si>
+  <si>
+    <t>S1395</t>
+  </si>
+  <si>
+    <t>S1396</t>
+  </si>
+  <si>
+    <t>S1397</t>
+  </si>
+  <si>
+    <t>S1398</t>
+  </si>
+  <si>
+    <t>S1399</t>
+  </si>
+  <si>
+    <t>S1400</t>
+  </si>
+  <si>
+    <t>S1401</t>
+  </si>
+  <si>
+    <t>S1402</t>
+  </si>
+  <si>
+    <t>S1403</t>
+  </si>
+  <si>
+    <t>S1404</t>
+  </si>
+  <si>
+    <t>S1405</t>
+  </si>
+  <si>
+    <t>S1406</t>
+  </si>
+  <si>
+    <t>S1407</t>
+  </si>
+  <si>
+    <t>S1408</t>
+  </si>
+  <si>
+    <t>S1409</t>
+  </si>
+  <si>
+    <t>S1410</t>
+  </si>
+  <si>
+    <t>S1411</t>
+  </si>
+  <si>
+    <t>S1412</t>
+  </si>
+  <si>
+    <t>S1413</t>
+  </si>
+  <si>
+    <t>S1414</t>
+  </si>
+  <si>
+    <t>S1415</t>
+  </si>
+  <si>
+    <t>S1416</t>
+  </si>
+  <si>
+    <t>S1417</t>
+  </si>
+  <si>
+    <t>S1418</t>
+  </si>
+  <si>
+    <t>S1419</t>
+  </si>
+  <si>
+    <t>S1420</t>
+  </si>
+  <si>
+    <t>S1421</t>
+  </si>
+  <si>
+    <t>S1422</t>
+  </si>
+  <si>
+    <t>S1423</t>
+  </si>
+  <si>
+    <t>S1424</t>
+  </si>
+  <si>
+    <t>S1425</t>
+  </si>
+  <si>
+    <t>S1426</t>
+  </si>
+  <si>
+    <t>S1427</t>
+  </si>
+  <si>
+    <t>S1428</t>
+  </si>
+  <si>
+    <t>S1429</t>
+  </si>
+  <si>
+    <t>S1430</t>
+  </si>
+  <si>
+    <t>S1431</t>
+  </si>
+  <si>
+    <t>S1432</t>
+  </si>
+  <si>
+    <t>S1433</t>
+  </si>
+  <si>
+    <t>S1434</t>
+  </si>
+  <si>
+    <t>S1435</t>
+  </si>
+  <si>
+    <t>S1436</t>
+  </si>
+  <si>
+    <t>S1437</t>
+  </si>
+  <si>
+    <t>S1438</t>
+  </si>
+  <si>
+    <t>S1439</t>
+  </si>
+  <si>
+    <t>S1440</t>
+  </si>
+  <si>
+    <t>S1441</t>
+  </si>
+  <si>
+    <t>S1442</t>
+  </si>
+  <si>
+    <t>S1443</t>
+  </si>
+  <si>
+    <t>S1444</t>
+  </si>
+  <si>
+    <t>S1445</t>
+  </si>
+  <si>
+    <t>S1446</t>
+  </si>
+  <si>
+    <t>S1447</t>
+  </si>
+  <si>
+    <t>S1448</t>
+  </si>
+  <si>
+    <t>S1449</t>
+  </si>
+  <si>
+    <t>S1450</t>
+  </si>
+  <si>
+    <t>S1451</t>
+  </si>
+  <si>
+    <t>S1452</t>
+  </si>
+  <si>
+    <t>S1453</t>
+  </si>
+  <si>
+    <t>S1454</t>
+  </si>
+  <si>
+    <t>S1455</t>
+  </si>
+  <si>
+    <t>S1456</t>
+  </si>
+  <si>
+    <t>S1457</t>
+  </si>
+  <si>
+    <t>S1458</t>
+  </si>
+  <si>
+    <t>S1459</t>
+  </si>
+  <si>
+    <t>S1460</t>
+  </si>
+  <si>
+    <t>S1461</t>
+  </si>
+  <si>
+    <t>S1462</t>
+  </si>
+  <si>
+    <t>S1463</t>
+  </si>
+  <si>
+    <t>S1464</t>
+  </si>
+  <si>
+    <t>S1465</t>
+  </si>
+  <si>
+    <t>S1466</t>
+  </si>
+  <si>
+    <t>S1467</t>
+  </si>
+  <si>
+    <t>S1468</t>
+  </si>
+  <si>
+    <t>S1469</t>
+  </si>
+  <si>
+    <t>S1470</t>
+  </si>
+  <si>
+    <t>S1471</t>
+  </si>
+  <si>
+    <t>S1472</t>
+  </si>
+  <si>
+    <t>S1473</t>
+  </si>
+  <si>
+    <t>S1474</t>
+  </si>
+  <si>
+    <t>S1475</t>
+  </si>
+  <si>
+    <t>S1476</t>
+  </si>
+  <si>
+    <t>S1477</t>
+  </si>
+  <si>
+    <t>S1478</t>
+  </si>
+  <si>
+    <t>S1479</t>
+  </si>
+  <si>
+    <t>S1480</t>
+  </si>
+  <si>
+    <t>S1481</t>
+  </si>
+  <si>
+    <t>S1482</t>
+  </si>
+  <si>
+    <t>S1483</t>
+  </si>
+  <si>
+    <t>S1484</t>
+  </si>
+  <si>
+    <t>S1485</t>
+  </si>
+  <si>
+    <t>S1486</t>
+  </si>
+  <si>
+    <t>S1487</t>
+  </si>
+  <si>
+    <t>S1488</t>
+  </si>
+  <si>
+    <t>S1489</t>
+  </si>
+  <si>
+    <t>S1490</t>
+  </si>
+  <si>
+    <t>S1491</t>
+  </si>
+  <si>
+    <t>S1492</t>
+  </si>
+  <si>
+    <t>S1493</t>
+  </si>
+  <si>
+    <t>S1494</t>
+  </si>
+  <si>
+    <t>S1495</t>
+  </si>
+  <si>
+    <t>S1496</t>
+  </si>
+  <si>
+    <t>S1497</t>
+  </si>
+  <si>
+    <t>S1498</t>
+  </si>
+  <si>
+    <t>S1499</t>
+  </si>
+  <si>
+    <t>S1500</t>
+  </si>
+  <si>
+    <t>S1501</t>
+  </si>
+  <si>
+    <t>S1502</t>
+  </si>
+  <si>
+    <t>S1503</t>
+  </si>
+  <si>
+    <t>S1504</t>
+  </si>
+  <si>
+    <t>S1505</t>
+  </si>
+  <si>
+    <t>S1506</t>
+  </si>
+  <si>
+    <t>S1507</t>
+  </si>
+  <si>
+    <t>S1508</t>
+  </si>
+  <si>
+    <t>S1509</t>
+  </si>
+  <si>
+    <t>S1510</t>
+  </si>
+  <si>
+    <t>S1511</t>
+  </si>
+  <si>
+    <t>S1512</t>
+  </si>
+  <si>
+    <t>S1513</t>
+  </si>
+  <si>
+    <t>S1514</t>
+  </si>
+  <si>
+    <t>S1515</t>
+  </si>
+  <si>
+    <t>S1516</t>
+  </si>
+  <si>
+    <t>S1517</t>
+  </si>
+  <si>
+    <t>S1518</t>
+  </si>
+  <si>
+    <t>S1519</t>
+  </si>
+  <si>
+    <t>S1520</t>
+  </si>
+  <si>
+    <t>S1521</t>
+  </si>
+  <si>
+    <t>S1522</t>
+  </si>
+  <si>
+    <t>S1523</t>
+  </si>
+  <si>
+    <t>S1524</t>
+  </si>
+  <si>
+    <t>S1525</t>
+  </si>
+  <si>
+    <t>S1526</t>
+  </si>
+  <si>
+    <t>S1527</t>
+  </si>
+  <si>
+    <t>S1528</t>
+  </si>
+  <si>
+    <t>S1529</t>
+  </si>
+  <si>
+    <t>S1530</t>
+  </si>
+  <si>
+    <t>S1531</t>
+  </si>
+  <si>
+    <t>S1532</t>
+  </si>
+  <si>
+    <t>S1533</t>
+  </si>
+  <si>
+    <t>S1534</t>
+  </si>
+  <si>
+    <t>S1535</t>
+  </si>
+  <si>
+    <t>S1536</t>
+  </si>
+  <si>
+    <t>S1537</t>
+  </si>
+  <si>
+    <t>S1538</t>
+  </si>
+  <si>
+    <t>S1539</t>
+  </si>
+  <si>
+    <t>S1540</t>
+  </si>
+  <si>
+    <t>S1541</t>
+  </si>
+  <si>
+    <t>S1542</t>
+  </si>
+  <si>
+    <t>S1543</t>
+  </si>
+  <si>
+    <t>S1544</t>
+  </si>
+  <si>
+    <t>S1545</t>
+  </si>
+  <si>
+    <t>S1546</t>
+  </si>
+  <si>
+    <t>S1547</t>
+  </si>
+  <si>
+    <t>S1548</t>
+  </si>
+  <si>
+    <t>S1549</t>
+  </si>
+  <si>
+    <t>S1550</t>
+  </si>
+  <si>
+    <t>S1551</t>
+  </si>
+  <si>
+    <t>S1552</t>
+  </si>
+  <si>
+    <t>S1553</t>
+  </si>
+  <si>
+    <t>S1554</t>
+  </si>
+  <si>
+    <t>S1555</t>
+  </si>
+  <si>
+    <t>S1556</t>
+  </si>
+  <si>
+    <t>S1557</t>
+  </si>
+  <si>
+    <t>S1558</t>
+  </si>
+  <si>
+    <t>S1559</t>
+  </si>
+  <si>
+    <t>S1560</t>
+  </si>
+  <si>
+    <t>S1561</t>
+  </si>
+  <si>
+    <t>S1562</t>
+  </si>
+  <si>
+    <t>S1563</t>
+  </si>
+  <si>
+    <t>S1564</t>
+  </si>
+  <si>
+    <t>S1565</t>
+  </si>
+  <si>
+    <t>S1566</t>
+  </si>
+  <si>
+    <t>S1567</t>
+  </si>
+  <si>
+    <t>S1568</t>
+  </si>
+  <si>
+    <t>S1569</t>
+  </si>
+  <si>
+    <t>S1570</t>
+  </si>
+  <si>
+    <t>S1571</t>
+  </si>
+  <si>
+    <t>S1572</t>
+  </si>
+  <si>
+    <t>S1573</t>
+  </si>
+  <si>
+    <t>S1574</t>
+  </si>
+  <si>
+    <t>S1575</t>
+  </si>
+  <si>
+    <t>S1576</t>
+  </si>
+  <si>
+    <t>S1577</t>
+  </si>
+  <si>
+    <t>S1578</t>
+  </si>
+  <si>
+    <t>S1579</t>
+  </si>
+  <si>
+    <t>S1580</t>
+  </si>
+  <si>
+    <t>S1581</t>
+  </si>
+  <si>
+    <t>S1582</t>
+  </si>
+  <si>
+    <t>S1583</t>
+  </si>
+  <si>
+    <t>S1584</t>
+  </si>
+  <si>
+    <t>S1585</t>
+  </si>
+  <si>
+    <t>S1586</t>
+  </si>
+  <si>
+    <t>S1587</t>
+  </si>
+  <si>
+    <t>S1588</t>
+  </si>
+  <si>
+    <t>S1589</t>
+  </si>
+  <si>
+    <t>S1590</t>
+  </si>
+  <si>
+    <t>S1591</t>
+  </si>
+  <si>
+    <t>S1592</t>
+  </si>
+  <si>
+    <t>S1593</t>
+  </si>
+  <si>
+    <t>S1594</t>
+  </si>
+  <si>
+    <t>S1595</t>
+  </si>
+  <si>
+    <t>S1596</t>
+  </si>
+  <si>
+    <t>S1597</t>
+  </si>
+  <si>
+    <t>S1598</t>
+  </si>
+  <si>
+    <t>S1599</t>
+  </si>
+  <si>
+    <t>S1600</t>
+  </si>
+  <si>
+    <t>S1601</t>
+  </si>
+  <si>
+    <t>S1602</t>
+  </si>
+  <si>
+    <t>S1603</t>
+  </si>
+  <si>
+    <t>S1604</t>
+  </si>
+  <si>
+    <t>S1605</t>
+  </si>
+  <si>
+    <t>S1606</t>
+  </si>
+  <si>
+    <t>S1607</t>
+  </si>
+  <si>
+    <t>S1608</t>
+  </si>
+  <si>
+    <t>S1609</t>
+  </si>
+  <si>
+    <t>S1610</t>
+  </si>
+  <si>
+    <t>S1611</t>
+  </si>
+  <si>
+    <t>S1612</t>
+  </si>
+  <si>
+    <t>S1613</t>
+  </si>
+  <si>
+    <t>S1614</t>
+  </si>
+  <si>
+    <t>S1615</t>
+  </si>
+  <si>
+    <t>S1616</t>
+  </si>
+  <si>
+    <t>S1617</t>
+  </si>
+  <si>
+    <t>S1618</t>
+  </si>
+  <si>
+    <t>S1619</t>
+  </si>
+  <si>
+    <t>S1620</t>
+  </si>
+  <si>
+    <t>S1621</t>
+  </si>
+  <si>
+    <t>S1622</t>
+  </si>
+  <si>
+    <t>S1623</t>
+  </si>
+  <si>
+    <t>S1624</t>
+  </si>
+  <si>
+    <t>S1625</t>
+  </si>
+  <si>
+    <t>S1626</t>
+  </si>
+  <si>
+    <t>S1627</t>
+  </si>
+  <si>
+    <t>S1628</t>
+  </si>
+  <si>
+    <t>S1629</t>
+  </si>
+  <si>
+    <t>S1630</t>
+  </si>
+  <si>
+    <t>S1631</t>
+  </si>
+  <si>
+    <t>S1632</t>
+  </si>
+  <si>
+    <t>S1633</t>
+  </si>
+  <si>
+    <t>S1634</t>
+  </si>
+  <si>
+    <t>S1635</t>
+  </si>
+  <si>
+    <t>S1636</t>
+  </si>
+  <si>
+    <t>S1637</t>
+  </si>
+  <si>
+    <t>S1638</t>
+  </si>
+  <si>
+    <t>S1639</t>
+  </si>
+  <si>
+    <t>S1640</t>
+  </si>
+  <si>
+    <t>S1641</t>
+  </si>
+  <si>
+    <t>S1642</t>
+  </si>
+  <si>
+    <t>S1643</t>
+  </si>
+  <si>
+    <t>S1644</t>
+  </si>
+  <si>
+    <t>S1645</t>
+  </si>
+  <si>
+    <t>S1646</t>
+  </si>
+  <si>
+    <t>S1647</t>
+  </si>
+  <si>
+    <t>S1648</t>
+  </si>
+  <si>
+    <t>S1649</t>
+  </si>
+  <si>
+    <t>S1650</t>
+  </si>
+  <si>
+    <t>S1651</t>
+  </si>
+  <si>
+    <t>S1652</t>
+  </si>
+  <si>
+    <t>S1653</t>
+  </si>
+  <si>
+    <t>S1654</t>
+  </si>
+  <si>
+    <t>S1655</t>
+  </si>
+  <si>
+    <t>S1656</t>
+  </si>
+  <si>
+    <t>S1657</t>
+  </si>
+  <si>
+    <t>S1658</t>
+  </si>
+  <si>
+    <t>S1659</t>
+  </si>
+  <si>
+    <t>S1660</t>
+  </si>
+  <si>
+    <t>S1661</t>
+  </si>
+  <si>
+    <t>S1662</t>
+  </si>
+  <si>
+    <t>S1663</t>
+  </si>
+  <si>
+    <t>S1664</t>
+  </si>
+  <si>
+    <t>S1665</t>
+  </si>
+  <si>
+    <t>S1666</t>
+  </si>
+  <si>
+    <t>S1667</t>
+  </si>
+  <si>
+    <t>S1668</t>
+  </si>
+  <si>
+    <t>S1669</t>
+  </si>
+  <si>
+    <t>S1670</t>
+  </si>
+  <si>
+    <t>S1671</t>
+  </si>
+  <si>
+    <t>S1672</t>
+  </si>
+  <si>
+    <t>S1673</t>
+  </si>
+  <si>
+    <t>S1674</t>
+  </si>
+  <si>
+    <t>S1675</t>
+  </si>
+  <si>
+    <t>S1676</t>
+  </si>
+  <si>
+    <t>S1677</t>
+  </si>
+  <si>
+    <t>S1678</t>
+  </si>
+  <si>
+    <t>S1679</t>
+  </si>
+  <si>
+    <t>S1680</t>
+  </si>
+  <si>
+    <t>S1681</t>
+  </si>
+  <si>
+    <t>S1682</t>
+  </si>
+  <si>
+    <t>S1683</t>
+  </si>
+  <si>
+    <t>S1684</t>
+  </si>
+  <si>
+    <t>S1685</t>
+  </si>
+  <si>
+    <t>S1686</t>
+  </si>
+  <si>
+    <t>S1687</t>
+  </si>
+  <si>
+    <t>S1688</t>
+  </si>
+  <si>
+    <t>S1689</t>
+  </si>
+  <si>
+    <t>S1690</t>
+  </si>
+  <si>
+    <t>S1691</t>
+  </si>
+  <si>
+    <t>S1692</t>
+  </si>
+  <si>
+    <t>S1693</t>
+  </si>
+  <si>
+    <t>S1694</t>
+  </si>
+  <si>
+    <t>S1695</t>
+  </si>
+  <si>
+    <t>S1696</t>
+  </si>
+  <si>
+    <t>S1697</t>
+  </si>
+  <si>
+    <t>S1698</t>
+  </si>
+  <si>
+    <t>S1699</t>
+  </si>
+  <si>
+    <t>S1700</t>
+  </si>
+  <si>
+    <t>S1701</t>
+  </si>
+  <si>
+    <t>S1702</t>
+  </si>
+  <si>
+    <t>S1703</t>
+  </si>
+  <si>
+    <t>S1704</t>
+  </si>
+  <si>
+    <t>S1705</t>
+  </si>
+  <si>
+    <t>S1706</t>
+  </si>
+  <si>
+    <t>S1707</t>
+  </si>
+  <si>
+    <t>S1708</t>
+  </si>
+  <si>
+    <t>S1709</t>
+  </si>
+  <si>
+    <t>S1710</t>
+  </si>
+  <si>
+    <t>S1711</t>
+  </si>
+  <si>
+    <t>S1712</t>
+  </si>
+  <si>
+    <t>S1713</t>
+  </si>
+  <si>
+    <t>S1714</t>
+  </si>
+  <si>
+    <t>S1715</t>
+  </si>
+  <si>
+    <t>S1716</t>
+  </si>
+  <si>
+    <t>S1717</t>
+  </si>
+  <si>
+    <t>S1718</t>
+  </si>
+  <si>
+    <t>S1719</t>
+  </si>
+  <si>
+    <t>S1720</t>
+  </si>
+  <si>
+    <t>S1721</t>
+  </si>
+  <si>
+    <t>S1722</t>
+  </si>
+  <si>
+    <t>UH123</t>
+  </si>
+  <si>
+    <t>X AKL 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X AKL 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X DKV_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X MPLB 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X MPLB 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X PM_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 3_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 4_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI AKL 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI AKL 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI DKV_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI MPLB 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI MPLB 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI PM_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 3_ULANGAN HARIAN_2526</t>
   </si>
 </sst>
 </file>
@@ -6163,16 +6163,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EC7F41-F6EF-E64F-BAAF-B3AB559FE08B}">
-  <dimension ref="A1:I1115"/>
+  <dimension ref="A1:I1114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -30662,15 +30662,6 @@
       <c r="F1114" s="1"/>
       <c r="G1114" s="1"/>
       <c r="H1114" s="1"/>
-    </row>
-    <row r="1115" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1115" s="1"/>
-      <c r="C1115" s="1"/>
-      <c r="D1115" s="1"/>
-      <c r="E1115" s="1"/>
-      <c r="F1115" s="1"/>
-      <c r="G1115" s="1"/>
-      <c r="H1115" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/temp_doc/PESERTA UJIAN FIX ADMIN.xlsx
+++ b/temp_doc/PESERTA UJIAN FIX ADMIN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70739AF-D98A-3441-87CD-704C9388CAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF6671-4FCF-F44C-BBCE-D27384E316CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A7D75AB7-B047-3448-8A7B-4FE35F9227AE}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16080" xr2:uid="{A7D75AB7-B047-3448-8A7B-4FE35F9227AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5992,7 +5992,7 @@
     <t>MUHAMMAD FAJAR MAULANA</t>
   </si>
   <si>
-    <t>XYJ513</t>
+    <t>KMH726</t>
   </si>
 </sst>
 </file>
@@ -6433,11 +6433,11 @@
       </c>
       <c r="J2" t="str">
         <f ca="1">CHAR(RANDBETWEEN(65,90))&amp;CHAR(RANDBETWEEN(65,90))&amp;CHAR(RANDBETWEEN(65,90))</f>
-        <v>DEB</v>
+        <v>FRI</v>
       </c>
       <c r="K2" t="str">
         <f ca="1">CONCATENATE(J2,RANDBETWEEN(111,999))</f>
-        <v>DEB433</v>
+        <v>FRI576</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
